--- a/artfynd/A 43942-2025 artfynd.xlsx
+++ b/artfynd/A 43942-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>368689</v>
       </c>
       <c r="B2" t="n">
-        <v>98007</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100856</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -720,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>547510.3210610425</v>
+        <v>547510</v>
       </c>
       <c r="R2" t="n">
-        <v>6605802.949429374</v>
+        <v>6605803</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -753,19 +748,9 @@
           <t>1996-07-02</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>1996-07-02</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -809,12 +794,7 @@
         <v>368690</v>
       </c>
       <c r="B3" t="n">
-        <v>98008</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>100856</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -851,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>547379.2022593515</v>
+        <v>547379</v>
       </c>
       <c r="R3" t="n">
-        <v>6605861.052907656</v>
+        <v>6605861</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,19 +864,9 @@
           <t>1996-07-02</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>1996-07-02</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -940,12 +910,7 @@
         <v>368691</v>
       </c>
       <c r="B4" t="n">
-        <v>98008</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>100856</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -982,10 +947,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>547498.9128815369</v>
+        <v>547499</v>
       </c>
       <c r="R4" t="n">
-        <v>6605902.576264138</v>
+        <v>6605903</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1015,19 +980,9 @@
           <t>1996-07-02</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>1996-07-02</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1065,6 +1020,125 @@
           <t>Uppföljning av skyddade områden</t>
         </is>
       </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>101358728</v>
+      </c>
+      <c r="B5" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Solbacken SV, Vstm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>547656</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6605728</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Köping</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Kolsva</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2022-06-02</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2022-06-02</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Utflykt med Malmaskolan i Kolsvas elever från mellanstadiet. Ett led i att få igång ett botanikintresse och allmän kännedom om vår natur.</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Kenneth Nordberg</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Kenneth Nordberg</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 43942-2025 artfynd.xlsx
+++ b/artfynd/A 43942-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -788,6 +793,11 @@
           <t>Uppföljning av skyddade områden</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/368689</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -904,6 +914,11 @@
           <t>Uppföljning av skyddade områden</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/368690</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1020,6 +1035,11 @@
           <t>Uppföljning av skyddade områden</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/368691</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1139,8 +1159,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101358728</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>